--- a/CPRD Raw Analysis/Results/Output_monthly_visits_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_monthly_visits_Raw.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -368,25 +368,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>sd_visits</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>q1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>median</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>q3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>n_pts</t>
         </is>
@@ -397,22 +407,28 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="C2">
-        <v>2.41</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>4</v>
       </c>
-      <c r="G2">
-        <v>19299</v>
+      <c r="I2">
+        <v>19034</v>
       </c>
     </row>
     <row r="3">
@@ -423,19 +439,25 @@
         <v>2.68</v>
       </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>25</v>
+      </c>
+      <c r="E3">
         <v>2.22</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>15876</v>
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>15872</v>
       </c>
     </row>
     <row r="4">
@@ -446,18 +468,24 @@
         <v>2.64</v>
       </c>
       <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>36</v>
+      </c>
+      <c r="E4">
         <v>2.2</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>14615</v>
       </c>
     </row>
@@ -469,18 +497,24 @@
         <v>2.54</v>
       </c>
       <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>32</v>
+      </c>
+      <c r="E5">
         <v>2.08</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
         <v>13625</v>
       </c>
     </row>
@@ -492,18 +526,24 @@
         <v>2.53</v>
       </c>
       <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>34</v>
+      </c>
+      <c r="E6">
         <v>2.12</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
       <c r="F6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
         <v>12723</v>
       </c>
     </row>
@@ -515,18 +555,24 @@
         <v>2.49</v>
       </c>
       <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>24</v>
+      </c>
+      <c r="E7">
         <v>2.05</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
       <c r="F7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
         <v>12233</v>
       </c>
     </row>
@@ -538,18 +584,24 @@
         <v>2.48</v>
       </c>
       <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
         <v>2.03</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
       <c r="F8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
         <v>11695</v>
       </c>
     </row>
@@ -561,18 +613,24 @@
         <v>2.42</v>
       </c>
       <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9">
         <v>1.98</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
       <c r="F9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9">
         <v>11347</v>
       </c>
     </row>
@@ -584,18 +642,24 @@
         <v>2.48</v>
       </c>
       <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>32</v>
+      </c>
+      <c r="E10">
         <v>2.03</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
       <c r="F10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="I10">
         <v>11155</v>
       </c>
     </row>
@@ -607,18 +671,24 @@
         <v>2.42</v>
       </c>
       <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>34</v>
+      </c>
+      <c r="E11">
         <v>1.96</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
       <c r="F11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
+      </c>
+      <c r="I11">
         <v>10900</v>
       </c>
     </row>
@@ -630,18 +700,24 @@
         <v>2.42</v>
       </c>
       <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>42</v>
+      </c>
+      <c r="E12">
         <v>1.97</v>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
       <c r="F12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12">
         <v>10696</v>
       </c>
     </row>
@@ -653,18 +729,24 @@
         <v>2.45</v>
       </c>
       <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>32</v>
+      </c>
+      <c r="E13">
         <v>2.01</v>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
       <c r="F13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
         <v>10585</v>
       </c>
     </row>
@@ -676,18 +758,24 @@
         <v>2.44</v>
       </c>
       <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>30</v>
+      </c>
+      <c r="E14">
         <v>1.96</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
       <c r="F14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
         <v>10438</v>
       </c>
     </row>
@@ -699,18 +787,24 @@
         <v>2.44</v>
       </c>
       <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>21</v>
+      </c>
+      <c r="E15">
         <v>1.97</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
       <c r="F15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
+      </c>
+      <c r="I15">
         <v>10096</v>
       </c>
     </row>
@@ -722,18 +816,24 @@
         <v>2.48</v>
       </c>
       <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>23</v>
+      </c>
+      <c r="E16">
         <v>2.04</v>
       </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>2</v>
-      </c>
       <c r="F16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16">
         <v>9940</v>
       </c>
     </row>
@@ -745,18 +845,24 @@
         <v>2.42</v>
       </c>
       <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>28</v>
+      </c>
+      <c r="E17">
         <v>1.98</v>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>2</v>
-      </c>
       <c r="F17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+      <c r="I17">
         <v>9820</v>
       </c>
     </row>
@@ -768,18 +874,24 @@
         <v>2.43</v>
       </c>
       <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>28</v>
+      </c>
+      <c r="E18">
         <v>1.95</v>
       </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
-        <v>2</v>
-      </c>
       <c r="F18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>3</v>
+      </c>
+      <c r="I18">
         <v>9735</v>
       </c>
     </row>
@@ -791,18 +903,24 @@
         <v>2.44</v>
       </c>
       <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>23</v>
+      </c>
+      <c r="E19">
         <v>2.02</v>
       </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>2</v>
-      </c>
       <c r="F19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
         <v>9606</v>
       </c>
     </row>
@@ -814,18 +932,24 @@
         <v>2.41</v>
       </c>
       <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>25</v>
+      </c>
+      <c r="E20">
         <v>1.96</v>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>2</v>
-      </c>
       <c r="F20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <v>3</v>
+      </c>
+      <c r="I20">
         <v>9591</v>
       </c>
     </row>
@@ -837,18 +961,24 @@
         <v>2.43</v>
       </c>
       <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>26</v>
+      </c>
+      <c r="E21">
         <v>1.99</v>
       </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
       <c r="F21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <v>3</v>
+      </c>
+      <c r="I21">
         <v>9411</v>
       </c>
     </row>
@@ -860,18 +990,24 @@
         <v>2.43</v>
       </c>
       <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>21</v>
+      </c>
+      <c r="E22">
         <v>1.98</v>
       </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>2</v>
-      </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>3</v>
+      </c>
+      <c r="I22">
         <v>9332</v>
       </c>
     </row>
@@ -883,18 +1019,24 @@
         <v>2.41</v>
       </c>
       <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>22</v>
+      </c>
+      <c r="E23">
         <v>1.93</v>
       </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
       <c r="F23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23">
         <v>9113</v>
       </c>
     </row>
@@ -906,18 +1048,24 @@
         <v>2.41</v>
       </c>
       <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>20</v>
+      </c>
+      <c r="E24">
         <v>1.93</v>
       </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24">
-        <v>2</v>
-      </c>
       <c r="F24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24">
         <v>9107</v>
       </c>
     </row>
@@ -929,18 +1077,24 @@
         <v>2.41</v>
       </c>
       <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>19</v>
+      </c>
+      <c r="E25">
         <v>1.96</v>
       </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25">
-        <v>2</v>
-      </c>
       <c r="F25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>3</v>
+      </c>
+      <c r="I25">
         <v>8906</v>
       </c>
     </row>
@@ -952,18 +1106,24 @@
         <v>1.07</v>
       </c>
       <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26">
         <v>0.27</v>
       </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
         <v>405</v>
       </c>
     </row>
@@ -974,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -990,25 +1150,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>sd_visits</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>q1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>median</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>q3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>n_pts</t>
         </is>
@@ -1019,22 +1189,28 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="C2">
-        <v>2.41</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2">
         <v>4</v>
       </c>
-      <c r="G2">
-        <v>19193</v>
+      <c r="I2">
+        <v>19034</v>
       </c>
     </row>
     <row r="3">
@@ -1045,18 +1221,24 @@
         <v>2.68</v>
       </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>25</v>
+      </c>
+      <c r="E3">
         <v>2.23</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
       <c r="F3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
         <v>15793</v>
       </c>
     </row>
@@ -1068,18 +1250,24 @@
         <v>2.64</v>
       </c>
       <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>36</v>
+      </c>
+      <c r="E4">
         <v>2.2</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
+      </c>
+      <c r="I4">
         <v>14544</v>
       </c>
     </row>
@@ -1091,18 +1279,24 @@
         <v>2.55</v>
       </c>
       <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>32</v>
+      </c>
+      <c r="E5">
         <v>2.08</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>3</v>
+      </c>
+      <c r="I5">
         <v>13433</v>
       </c>
     </row>
@@ -1114,18 +1308,24 @@
         <v>2.54</v>
       </c>
       <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>34</v>
+      </c>
+      <c r="E6">
         <v>2.12</v>
       </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
       <c r="F6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
         <v>12599</v>
       </c>
     </row>
@@ -1137,18 +1337,24 @@
         <v>2.49</v>
       </c>
       <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>24</v>
+      </c>
+      <c r="E7">
         <v>2.06</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
       <c r="F7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
         <v>12120</v>
       </c>
     </row>
@@ -1160,18 +1366,24 @@
         <v>2.48</v>
       </c>
       <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
         <v>2.03</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
       <c r="F8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8">
         <v>11620</v>
       </c>
     </row>
@@ -1183,18 +1395,24 @@
         <v>2.43</v>
       </c>
       <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9">
         <v>1.99</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
       <c r="F9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>3</v>
+      </c>
+      <c r="I9">
         <v>11261</v>
       </c>
     </row>
@@ -1206,18 +1424,24 @@
         <v>2.48</v>
       </c>
       <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>32</v>
+      </c>
+      <c r="E10">
         <v>2.03</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
       <c r="F10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="I10">
         <v>11084</v>
       </c>
     </row>
@@ -1229,18 +1453,24 @@
         <v>2.43</v>
       </c>
       <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>34</v>
+      </c>
+      <c r="E11">
         <v>1.96</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
       <c r="F11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11">
+        <v>3</v>
+      </c>
+      <c r="I11">
         <v>10842</v>
       </c>
     </row>
@@ -1252,18 +1482,24 @@
         <v>2.43</v>
       </c>
       <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>42</v>
+      </c>
+      <c r="E12">
         <v>1.97</v>
       </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
       <c r="F12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12">
         <v>10638</v>
       </c>
     </row>
@@ -1275,18 +1511,24 @@
         <v>2.45</v>
       </c>
       <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>32</v>
+      </c>
+      <c r="E13">
         <v>2.01</v>
       </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
       <c r="F13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
         <v>10523</v>
       </c>
     </row>
@@ -1298,18 +1540,24 @@
         <v>2.44</v>
       </c>
       <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>30</v>
+      </c>
+      <c r="E14">
         <v>1.97</v>
       </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
       <c r="F14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
         <v>10386</v>
       </c>
     </row>
@@ -1321,18 +1569,24 @@
         <v>2.44</v>
       </c>
       <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>21</v>
+      </c>
+      <c r="E15">
         <v>1.97</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
       <c r="F15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
+      </c>
+      <c r="I15">
         <v>10054</v>
       </c>
     </row>
@@ -1344,18 +1598,24 @@
         <v>2.48</v>
       </c>
       <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>23</v>
+      </c>
+      <c r="E16">
         <v>2.04</v>
       </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>2</v>
-      </c>
       <c r="F16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16">
         <v>9895</v>
       </c>
     </row>
@@ -1367,18 +1627,24 @@
         <v>2.42</v>
       </c>
       <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>28</v>
+      </c>
+      <c r="E17">
         <v>1.97</v>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>2</v>
-      </c>
       <c r="F17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+      <c r="I17">
         <v>9771</v>
       </c>
     </row>
@@ -1390,18 +1656,24 @@
         <v>2.43</v>
       </c>
       <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>28</v>
+      </c>
+      <c r="E18">
         <v>1.95</v>
       </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
-        <v>2</v>
-      </c>
       <c r="F18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>3</v>
+      </c>
+      <c r="I18">
         <v>9692</v>
       </c>
     </row>
@@ -1413,18 +1685,24 @@
         <v>2.44</v>
       </c>
       <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>23</v>
+      </c>
+      <c r="E19">
         <v>2.03</v>
       </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>2</v>
-      </c>
       <c r="F19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19">
         <v>9561</v>
       </c>
     </row>
@@ -1436,18 +1714,24 @@
         <v>2.41</v>
       </c>
       <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>25</v>
+      </c>
+      <c r="E20">
         <v>1.96</v>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>2</v>
-      </c>
       <c r="F20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20">
+        <v>2</v>
+      </c>
+      <c r="H20">
+        <v>3</v>
+      </c>
+      <c r="I20">
         <v>9552</v>
       </c>
     </row>
@@ -1459,18 +1743,24 @@
         <v>2.43</v>
       </c>
       <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>26</v>
+      </c>
+      <c r="E21">
         <v>1.99</v>
       </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>2</v>
-      </c>
       <c r="F21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21">
+        <v>2</v>
+      </c>
+      <c r="H21">
+        <v>3</v>
+      </c>
+      <c r="I21">
         <v>9369</v>
       </c>
     </row>
@@ -1482,18 +1772,24 @@
         <v>2.43</v>
       </c>
       <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>21</v>
+      </c>
+      <c r="E22">
         <v>1.98</v>
       </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>2</v>
-      </c>
       <c r="F22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22">
+        <v>2</v>
+      </c>
+      <c r="H22">
+        <v>3</v>
+      </c>
+      <c r="I22">
         <v>9293</v>
       </c>
     </row>
@@ -1505,18 +1801,24 @@
         <v>2.41</v>
       </c>
       <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>22</v>
+      </c>
+      <c r="E23">
         <v>1.94</v>
       </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
       <c r="F23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="I23">
         <v>9066</v>
       </c>
     </row>
@@ -1528,18 +1830,24 @@
         <v>2.42</v>
       </c>
       <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>20</v>
+      </c>
+      <c r="E24">
         <v>1.93</v>
       </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24">
-        <v>2</v>
-      </c>
       <c r="F24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24">
+        <v>3</v>
+      </c>
+      <c r="I24">
         <v>9079</v>
       </c>
     </row>
@@ -1551,18 +1859,24 @@
         <v>2.42</v>
       </c>
       <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>19</v>
+      </c>
+      <c r="E25">
         <v>1.96</v>
       </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25">
-        <v>2</v>
-      </c>
       <c r="F25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>3</v>
+      </c>
+      <c r="I25">
         <v>8866</v>
       </c>
     </row>
@@ -1574,18 +1888,24 @@
         <v>1</v>
       </c>
       <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
         <v>0</v>
       </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
         <v>9</v>
       </c>
     </row>

--- a/CPRD Raw Analysis/Results/Output_monthly_visits_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_monthly_visits_Raw.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -404,10 +404,10 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -416,7 +416,7 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -428,15 +428,15 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <v>19034</v>
+        <v>19110</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -445,7 +445,7 @@
         <v>25</v>
       </c>
       <c r="E3">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -457,15 +457,15 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>15872</v>
+        <v>15773</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -474,7 +474,7 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -486,24 +486,24 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>14615</v>
+        <v>14724</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -515,15 +515,15 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>13625</v>
+        <v>13502</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -532,7 +532,7 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -544,15 +544,15 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>12723</v>
+        <v>12822</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -561,7 +561,7 @@
         <v>24</v>
       </c>
       <c r="E7">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -573,24 +573,24 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>12233</v>
+        <v>12157</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E8">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -602,15 +602,15 @@
         <v>3</v>
       </c>
       <c r="I8">
-        <v>11695</v>
+        <v>11772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -619,7 +619,7 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -631,24 +631,24 @@
         <v>3</v>
       </c>
       <c r="I9">
-        <v>11347</v>
+        <v>11232</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -660,24 +660,24 @@
         <v>3</v>
       </c>
       <c r="I10">
-        <v>11155</v>
+        <v>11129</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E11">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -689,24 +689,24 @@
         <v>3</v>
       </c>
       <c r="I11">
-        <v>10900</v>
+        <v>10982</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -718,24 +718,24 @@
         <v>3</v>
       </c>
       <c r="I12">
-        <v>10696</v>
+        <v>10611</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -747,24 +747,24 @@
         <v>3</v>
       </c>
       <c r="I13">
-        <v>10585</v>
+        <v>10692</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -776,24 +776,24 @@
         <v>3</v>
       </c>
       <c r="I14">
-        <v>10438</v>
+        <v>10348</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E15">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -805,15 +805,15 @@
         <v>3</v>
       </c>
       <c r="I15">
-        <v>10096</v>
+        <v>10184</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -822,7 +822,7 @@
         <v>23</v>
       </c>
       <c r="E16">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -834,15 +834,15 @@
         <v>3</v>
       </c>
       <c r="I16">
-        <v>9940</v>
+        <v>9852</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -851,7 +851,7 @@
         <v>28</v>
       </c>
       <c r="E17">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -863,15 +863,15 @@
         <v>3</v>
       </c>
       <c r="I17">
-        <v>9820</v>
+        <v>9897</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -880,7 +880,7 @@
         <v>28</v>
       </c>
       <c r="E18">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -892,24 +892,24 @@
         <v>3</v>
       </c>
       <c r="I18">
-        <v>9735</v>
+        <v>9671</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E19">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -921,15 +921,15 @@
         <v>3</v>
       </c>
       <c r="I19">
-        <v>9606</v>
+        <v>9573</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>25</v>
       </c>
       <c r="E20">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -950,15 +950,15 @@
         <v>3</v>
       </c>
       <c r="I20">
-        <v>9591</v>
+        <v>9650</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -967,7 +967,7 @@
         <v>26</v>
       </c>
       <c r="E21">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -979,15 +979,15 @@
         <v>3</v>
       </c>
       <c r="I21">
-        <v>9411</v>
+        <v>9355</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -996,7 +996,7 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1008,24 +1008,24 @@
         <v>3</v>
       </c>
       <c r="I22">
-        <v>9332</v>
+        <v>9422</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>2.4</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
         <v>21</v>
       </c>
-      <c r="B23">
-        <v>2.41</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>22</v>
-      </c>
       <c r="E23">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -1037,15 +1037,15 @@
         <v>3</v>
       </c>
       <c r="I23">
-        <v>9113</v>
+        <v>9028</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>20</v>
       </c>
       <c r="E24">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1066,15 +1066,15 @@
         <v>3</v>
       </c>
       <c r="I24">
-        <v>9107</v>
+        <v>9230</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1083,7 +1083,7 @@
         <v>19</v>
       </c>
       <c r="E25">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -1095,36 +1095,7 @@
         <v>3</v>
       </c>
       <c r="I25">
-        <v>8906</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26">
-        <v>1.07</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>3</v>
-      </c>
-      <c r="E26">
-        <v>0.27</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26">
-        <v>405</v>
+        <v>8767</v>
       </c>
     </row>
   </sheetData>
@@ -1134,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1186,10 +1157,10 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1198,7 +1169,7 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1210,15 +1181,15 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <v>19034</v>
+        <v>19110</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1227,7 +1198,7 @@
         <v>25</v>
       </c>
       <c r="E3">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1239,15 +1210,15 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>15793</v>
+        <v>15561</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1256,7 +1227,7 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1268,24 +1239,24 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>14544</v>
+        <v>14529</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1297,15 +1268,15 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>13433</v>
+        <v>13125</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1314,7 +1285,7 @@
         <v>34</v>
       </c>
       <c r="E6">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1326,15 +1297,15 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>12599</v>
+        <v>12545</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1343,7 +1314,7 @@
         <v>24</v>
       </c>
       <c r="E7">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1355,24 +1326,24 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>12120</v>
+        <v>11939</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E8">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1384,15 +1355,15 @@
         <v>3</v>
       </c>
       <c r="I8">
-        <v>11620</v>
+        <v>11581</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1401,7 +1372,7 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1413,24 +1384,24 @@
         <v>3</v>
       </c>
       <c r="I9">
-        <v>11261</v>
+        <v>11061</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1442,24 +1413,24 @@
         <v>3</v>
       </c>
       <c r="I10">
-        <v>11084</v>
+        <v>10977</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E11">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1471,24 +1442,24 @@
         <v>3</v>
       </c>
       <c r="I11">
-        <v>10842</v>
+        <v>10839</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1500,24 +1471,24 @@
         <v>3</v>
       </c>
       <c r="I12">
-        <v>10638</v>
+        <v>10496</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1529,24 +1500,24 @@
         <v>3</v>
       </c>
       <c r="I13">
-        <v>10523</v>
+        <v>10537</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1558,24 +1529,24 @@
         <v>3</v>
       </c>
       <c r="I14">
-        <v>10386</v>
+        <v>10227</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E15">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1587,15 +1558,15 @@
         <v>3</v>
       </c>
       <c r="I15">
-        <v>10054</v>
+        <v>10070</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1604,7 +1575,7 @@
         <v>23</v>
       </c>
       <c r="E16">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -1616,15 +1587,15 @@
         <v>3</v>
       </c>
       <c r="I16">
-        <v>9895</v>
+        <v>9748</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1633,7 +1604,7 @@
         <v>28</v>
       </c>
       <c r="E17">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1645,15 +1616,15 @@
         <v>3</v>
       </c>
       <c r="I17">
-        <v>9771</v>
+        <v>9788</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1662,7 +1633,7 @@
         <v>28</v>
       </c>
       <c r="E18">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -1674,24 +1645,24 @@
         <v>3</v>
       </c>
       <c r="I18">
-        <v>9692</v>
+        <v>9575</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E19">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1703,15 +1674,15 @@
         <v>3</v>
       </c>
       <c r="I19">
-        <v>9561</v>
+        <v>9471</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1720,7 +1691,7 @@
         <v>25</v>
       </c>
       <c r="E20">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1732,15 +1703,15 @@
         <v>3</v>
       </c>
       <c r="I20">
-        <v>9552</v>
+        <v>9557</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1749,7 +1720,7 @@
         <v>26</v>
       </c>
       <c r="E21">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -1761,15 +1732,15 @@
         <v>3</v>
       </c>
       <c r="I21">
-        <v>9369</v>
+        <v>9259</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1778,7 +1749,7 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1790,24 +1761,24 @@
         <v>3</v>
       </c>
       <c r="I22">
-        <v>9293</v>
+        <v>9327</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>2.4</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
         <v>21</v>
       </c>
-      <c r="B23">
-        <v>2.41</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>22</v>
-      </c>
       <c r="E23">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -1819,15 +1790,15 @@
         <v>3</v>
       </c>
       <c r="I23">
-        <v>9066</v>
+        <v>8935</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1836,7 +1807,7 @@
         <v>20</v>
       </c>
       <c r="E24">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1848,65 +1819,7 @@
         <v>3</v>
       </c>
       <c r="I24">
-        <v>9079</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25">
-        <v>2.42</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>19</v>
-      </c>
-      <c r="E25">
-        <v>1.96</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>2</v>
-      </c>
-      <c r="H25">
-        <v>3</v>
-      </c>
-      <c r="I25">
-        <v>8866</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26">
-        <v>9</v>
+        <v>9150</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_monthly_visits_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_monthly_visits_Raw.xlsx
@@ -1105,7 +1105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1189,16 +1189,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D3">
         <v>25</v>
       </c>
       <c r="E3">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1210,7 +1210,7 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>15561</v>
+        <v>15696</v>
       </c>
     </row>
     <row r="4">
@@ -1218,16 +1218,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D4">
         <v>36</v>
       </c>
       <c r="E4">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1239,7 +1239,7 @@
         <v>3</v>
       </c>
       <c r="I4">
-        <v>14529</v>
+        <v>14650</v>
       </c>
     </row>
     <row r="5">
@@ -1247,16 +1247,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D5">
         <v>34</v>
       </c>
       <c r="E5">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1268,7 +1268,7 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>13125</v>
+        <v>13324</v>
       </c>
     </row>
     <row r="6">
@@ -1276,10 +1276,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D6">
         <v>34</v>
@@ -1297,7 +1297,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>12545</v>
+        <v>12700</v>
       </c>
     </row>
     <row r="7">
@@ -1305,10 +1305,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D7">
         <v>24</v>
@@ -1326,7 +1326,7 @@
         <v>3</v>
       </c>
       <c r="I7">
-        <v>11939</v>
+        <v>12058</v>
       </c>
     </row>
     <row r="8">
@@ -1334,16 +1334,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D8">
         <v>29</v>
       </c>
       <c r="E8">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1355,7 +1355,7 @@
         <v>3</v>
       </c>
       <c r="I8">
-        <v>11581</v>
+        <v>11690</v>
       </c>
     </row>
     <row r="9">
@@ -1363,16 +1363,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D9">
         <v>30</v>
       </c>
       <c r="E9">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1384,7 +1384,7 @@
         <v>3</v>
       </c>
       <c r="I9">
-        <v>11061</v>
+        <v>11164</v>
       </c>
     </row>
     <row r="10">
@@ -1392,10 +1392,10 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D10">
         <v>31</v>
@@ -1413,7 +1413,7 @@
         <v>3</v>
       </c>
       <c r="I10">
-        <v>10977</v>
+        <v>11057</v>
       </c>
     </row>
     <row r="11">
@@ -1421,10 +1421,10 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D11">
         <v>36</v>
@@ -1442,7 +1442,7 @@
         <v>3</v>
       </c>
       <c r="I11">
-        <v>10839</v>
+        <v>10918</v>
       </c>
     </row>
     <row r="12">
@@ -1453,13 +1453,13 @@
         <v>2.41</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D12">
         <v>41</v>
       </c>
       <c r="E12">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1471,7 +1471,7 @@
         <v>3</v>
       </c>
       <c r="I12">
-        <v>10496</v>
+        <v>10558</v>
       </c>
     </row>
     <row r="13">
@@ -1479,16 +1479,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D13">
         <v>33</v>
       </c>
       <c r="E13">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1500,7 +1500,7 @@
         <v>3</v>
       </c>
       <c r="I13">
-        <v>10537</v>
+        <v>10640</v>
       </c>
     </row>
     <row r="14">
@@ -1508,16 +1508,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D14">
         <v>29</v>
       </c>
       <c r="E14">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -1529,7 +1529,7 @@
         <v>3</v>
       </c>
       <c r="I14">
-        <v>10227</v>
+        <v>10304</v>
       </c>
     </row>
     <row r="15">
@@ -1540,13 +1540,13 @@
         <v>2.46</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0.0012</v>
       </c>
       <c r="D15">
         <v>22</v>
       </c>
       <c r="E15">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1558,7 +1558,7 @@
         <v>3</v>
       </c>
       <c r="I15">
-        <v>10070</v>
+        <v>10139</v>
       </c>
     </row>
     <row r="16">
@@ -1566,10 +1566,10 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D16">
         <v>23</v>
@@ -1587,7 +1587,7 @@
         <v>3</v>
       </c>
       <c r="I16">
-        <v>9748</v>
+        <v>9820</v>
       </c>
     </row>
     <row r="17">
@@ -1595,16 +1595,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D17">
         <v>28</v>
       </c>
       <c r="E17">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -1616,7 +1616,7 @@
         <v>3</v>
       </c>
       <c r="I17">
-        <v>9788</v>
+        <v>9849</v>
       </c>
     </row>
     <row r="18">
@@ -1627,13 +1627,13 @@
         <v>2.41</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D18">
         <v>28</v>
       </c>
       <c r="E18">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>3</v>
       </c>
       <c r="I18">
-        <v>9575</v>
+        <v>9635</v>
       </c>
     </row>
     <row r="19">
@@ -1653,16 +1653,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D19">
         <v>21</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -1674,7 +1674,7 @@
         <v>3</v>
       </c>
       <c r="I19">
-        <v>9471</v>
+        <v>9531</v>
       </c>
     </row>
     <row r="20">
@@ -1682,10 +1682,10 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D20">
         <v>25</v>
@@ -1703,7 +1703,7 @@
         <v>3</v>
       </c>
       <c r="I20">
-        <v>9557</v>
+        <v>9608</v>
       </c>
     </row>
     <row r="21">
@@ -1711,10 +1711,10 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0.0012</v>
       </c>
       <c r="D21">
         <v>26</v>
@@ -1732,7 +1732,7 @@
         <v>3</v>
       </c>
       <c r="I21">
-        <v>9259</v>
+        <v>9319</v>
       </c>
     </row>
     <row r="22">
@@ -1743,13 +1743,13 @@
         <v>2.45</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D22">
         <v>21</v>
       </c>
       <c r="E22">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1761,7 +1761,7 @@
         <v>3</v>
       </c>
       <c r="I22">
-        <v>9327</v>
+        <v>9393</v>
       </c>
     </row>
     <row r="23">
@@ -1769,10 +1769,10 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D23">
         <v>21</v>
@@ -1790,7 +1790,7 @@
         <v>3</v>
       </c>
       <c r="I23">
-        <v>8935</v>
+        <v>8990</v>
       </c>
     </row>
     <row r="24">
@@ -1801,13 +1801,13 @@
         <v>2.44</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0.0011</v>
       </c>
       <c r="D24">
         <v>20</v>
       </c>
       <c r="E24">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -1819,7 +1819,36 @@
         <v>3</v>
       </c>
       <c r="I24">
-        <v>9150</v>
+        <v>9205</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>2.39</v>
+      </c>
+      <c r="C25">
+        <v>0.0011</v>
+      </c>
+      <c r="D25">
+        <v>19</v>
+      </c>
+      <c r="E25">
+        <v>1.93</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25">
+        <v>3</v>
+      </c>
+      <c r="I25">
+        <v>8744</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_monthly_visits_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_monthly_visits_Raw.xlsx
@@ -368,12 +368,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>min_visits</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>max_visits</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -383,17 +383,17 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>q1</t>
+          <t>q1_visits</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>median_visits</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>q3</t>
+          <t>q3_visits</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -407,28 +407,28 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3.12</v>
+        <v>2.18</v>
       </c>
       <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>24</v>
+      </c>
+      <c r="E2">
+        <v>2.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="D2">
-        <v>30</v>
-      </c>
-      <c r="E2">
-        <v>2.44</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
       <c r="H2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>19110</v>
+        <v>18133</v>
       </c>
     </row>
     <row r="3">
@@ -436,28 +436,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.66</v>
+        <v>1.54</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>25</v>
       </c>
       <c r="E3">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>15773</v>
+        <v>16127</v>
       </c>
     </row>
     <row r="4">
@@ -465,28 +465,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2.67</v>
+        <v>1.5</v>
       </c>
       <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>30</v>
+      </c>
+      <c r="E4">
+        <v>2.1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
-      <c r="D4">
-        <v>36</v>
-      </c>
-      <c r="E4">
-        <v>2.23</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
       <c r="H4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>14724</v>
+        <v>15209</v>
       </c>
     </row>
     <row r="5">
@@ -494,28 +494,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.52</v>
+        <v>1.34</v>
       </c>
       <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>30</v>
+      </c>
+      <c r="E5">
+        <v>1.92</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="D5">
-        <v>34</v>
-      </c>
-      <c r="E5">
-        <v>2.05</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>13502</v>
+        <v>14714</v>
       </c>
     </row>
     <row r="6">
@@ -523,28 +523,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2.55</v>
+        <v>1.34</v>
       </c>
       <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
-      <c r="D6">
-        <v>34</v>
-      </c>
-      <c r="E6">
-        <v>2.14</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
       <c r="H6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>12822</v>
+        <v>14372</v>
       </c>
     </row>
     <row r="7">
@@ -552,28 +552,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.47</v>
+        <v>1.27</v>
       </c>
       <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>21</v>
+      </c>
+      <c r="E7">
+        <v>1.91</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
-      <c r="D7">
-        <v>24</v>
-      </c>
-      <c r="E7">
-        <v>2.03</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
       <c r="H7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>12157</v>
+        <v>14099</v>
       </c>
     </row>
     <row r="8">
@@ -581,28 +581,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.5</v>
+        <v>1.26</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>29</v>
       </c>
       <c r="E8">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
       <c r="H8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>11772</v>
+        <v>13856</v>
       </c>
     </row>
     <row r="9">
@@ -610,28 +610,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2.41</v>
+        <v>1.17</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E9">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>11232</v>
+        <v>13637</v>
       </c>
     </row>
     <row r="10">
@@ -639,28 +639,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2.46</v>
+        <v>1.22</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E10">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>11129</v>
+        <v>13467</v>
       </c>
     </row>
     <row r="11">
@@ -668,28 +668,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2.44</v>
+        <v>1.2</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E11">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>10982</v>
+        <v>13293</v>
       </c>
     </row>
     <row r="12">
@@ -697,28 +697,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2.41</v>
+        <v>1.17</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>41</v>
       </c>
       <c r="E12">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>10611</v>
+        <v>13148</v>
       </c>
     </row>
     <row r="13">
@@ -726,28 +726,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>2.48</v>
+        <v>1.22</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>33</v>
       </c>
       <c r="E13">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>10692</v>
+        <v>12982</v>
       </c>
     </row>
     <row r="14">
@@ -755,28 +755,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>2.42</v>
+        <v>1.18</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E14">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I14">
-        <v>10348</v>
+        <v>12827</v>
       </c>
     </row>
     <row r="15">
@@ -784,28 +784,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>2.47</v>
+        <v>1.18</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>10184</v>
+        <v>12673</v>
       </c>
     </row>
     <row r="16">
@@ -813,28 +813,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2.46</v>
+        <v>1.15</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E16">
-        <v>2.03</v>
+        <v>1.84</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>9852</v>
+        <v>12547</v>
       </c>
     </row>
     <row r="17">
@@ -842,28 +842,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>2.43</v>
+        <v>1.14</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E17">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>9897</v>
+        <v>12416</v>
       </c>
     </row>
     <row r="18">
@@ -871,28 +871,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>2.42</v>
+        <v>1.12</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E18">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>9671</v>
+        <v>12295</v>
       </c>
     </row>
     <row r="19">
@@ -900,28 +900,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>2.42</v>
+        <v>1.14</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>9573</v>
+        <v>12163</v>
       </c>
     </row>
     <row r="20">
@@ -929,28 +929,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>2.43</v>
+        <v>1.15</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>25</v>
       </c>
       <c r="E20">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20">
-        <v>9650</v>
+        <v>12053</v>
       </c>
     </row>
     <row r="21">
@@ -958,28 +958,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>2.41</v>
+        <v>1.1</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E21">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>9355</v>
+        <v>11918</v>
       </c>
     </row>
     <row r="22">
@@ -987,28 +987,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2.46</v>
+        <v>1.15</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>21</v>
       </c>
       <c r="E22">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>9422</v>
+        <v>11788</v>
       </c>
     </row>
     <row r="23">
@@ -1016,28 +1016,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>2.4</v>
+        <v>1.09</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>21</v>
       </c>
       <c r="E23">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>9028</v>
+        <v>11667</v>
       </c>
     </row>
     <row r="24">
@@ -1045,28 +1045,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2.45</v>
+        <v>1.15</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E24">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>9230</v>
+        <v>11550</v>
       </c>
     </row>
     <row r="25">
@@ -1074,28 +1074,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>2.39</v>
+        <v>1.07</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E25">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <v>8767</v>
+        <v>7477</v>
       </c>
     </row>
   </sheetData>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>mean_visits</t>
+          <t>mean</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>sd_visits</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1160,16 +1160,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3.12</v>
+        <v>2.24</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1178,10 +1178,10 @@
         <v>2</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>19110</v>
+        <v>17639</v>
       </c>
     </row>
     <row r="3">
@@ -1189,28 +1189,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.65</v>
+        <v>1.61</v>
       </c>
       <c r="C3">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>25</v>
       </c>
       <c r="E3">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>15696</v>
+        <v>16635</v>
       </c>
     </row>
     <row r="4">
@@ -1218,28 +1218,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2.66</v>
+        <v>1.54</v>
       </c>
       <c r="C4">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
       <c r="H4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>14650</v>
+        <v>15411</v>
       </c>
     </row>
     <row r="5">
@@ -1247,28 +1247,28 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.5</v>
+        <v>1.37</v>
       </c>
       <c r="C5">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5">
-        <v>13324</v>
+        <v>14795</v>
       </c>
     </row>
     <row r="6">
@@ -1276,28 +1276,28 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2.53</v>
+        <v>1.37</v>
       </c>
       <c r="C6">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
       <c r="H6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>12700</v>
+        <v>14421</v>
       </c>
     </row>
     <row r="7">
@@ -1305,28 +1305,28 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>2.46</v>
+        <v>1.29</v>
       </c>
       <c r="C7">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E7">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
       <c r="H7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>12058</v>
+        <v>14123</v>
       </c>
     </row>
     <row r="8">
@@ -1334,28 +1334,28 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2.49</v>
+        <v>1.28</v>
       </c>
       <c r="C8">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>29</v>
       </c>
       <c r="E8">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
       <c r="H8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>11690</v>
+        <v>13862</v>
       </c>
     </row>
     <row r="9">
@@ -1363,28 +1363,28 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>2.4</v>
+        <v>1.19</v>
       </c>
       <c r="C9">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E9">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>11164</v>
+        <v>13634</v>
       </c>
     </row>
     <row r="10">
@@ -1392,28 +1392,28 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>2.45</v>
+        <v>1.24</v>
       </c>
       <c r="C10">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E10">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
       <c r="H10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>11057</v>
+        <v>13445</v>
       </c>
     </row>
     <row r="11">
@@ -1421,28 +1421,28 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2.43</v>
+        <v>1.22</v>
       </c>
       <c r="C11">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="E11">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>10918</v>
+        <v>13270</v>
       </c>
     </row>
     <row r="12">
@@ -1450,28 +1450,28 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>2.41</v>
+        <v>1.18</v>
       </c>
       <c r="C12">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>41</v>
       </c>
       <c r="E12">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>10558</v>
+        <v>13122</v>
       </c>
     </row>
     <row r="13">
@@ -1479,28 +1479,28 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>2.47</v>
+        <v>1.24</v>
       </c>
       <c r="C13">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>33</v>
       </c>
       <c r="E13">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
         <v>1</v>
       </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
       <c r="H13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>10640</v>
+        <v>12979</v>
       </c>
     </row>
     <row r="14">
@@ -1508,28 +1508,28 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>2.41</v>
+        <v>1.19</v>
       </c>
       <c r="C14">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E14">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I14">
-        <v>10304</v>
+        <v>12801</v>
       </c>
     </row>
     <row r="15">
@@ -1537,28 +1537,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>2.46</v>
+        <v>1.2</v>
       </c>
       <c r="C15">
-        <v>0.0012</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>10139</v>
+        <v>12662</v>
       </c>
     </row>
     <row r="16">
@@ -1566,28 +1566,28 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>2.45</v>
+        <v>1.17</v>
       </c>
       <c r="C16">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E16">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>9820</v>
+        <v>12520</v>
       </c>
     </row>
     <row r="17">
@@ -1595,28 +1595,28 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>2.42</v>
+        <v>1.16</v>
       </c>
       <c r="C17">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E17">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>9849</v>
+        <v>12388</v>
       </c>
     </row>
     <row r="18">
@@ -1624,28 +1624,28 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>2.41</v>
+        <v>1.13</v>
       </c>
       <c r="C18">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E18">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>9635</v>
+        <v>12259</v>
       </c>
     </row>
     <row r="19">
@@ -1653,28 +1653,28 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>2.41</v>
+        <v>1.16</v>
       </c>
       <c r="C19">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E19">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>9531</v>
+        <v>12135</v>
       </c>
     </row>
     <row r="20">
@@ -1682,28 +1682,28 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>2.42</v>
+        <v>1.17</v>
       </c>
       <c r="C20">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>25</v>
       </c>
       <c r="E20">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20">
-        <v>9608</v>
+        <v>12020</v>
       </c>
     </row>
     <row r="21">
@@ -1711,28 +1711,28 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>2.4</v>
+        <v>1.12</v>
       </c>
       <c r="C21">
-        <v>0.0012</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E21">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>9319</v>
+        <v>11903</v>
       </c>
     </row>
     <row r="22">
@@ -1740,28 +1740,28 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2.45</v>
+        <v>1.17</v>
       </c>
       <c r="C22">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>21</v>
       </c>
       <c r="E22">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>9393</v>
+        <v>11776</v>
       </c>
     </row>
     <row r="23">
@@ -1769,28 +1769,28 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>2.39</v>
+        <v>1.1</v>
       </c>
       <c r="C23">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>21</v>
       </c>
       <c r="E23">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>8990</v>
+        <v>11637</v>
       </c>
     </row>
     <row r="24">
@@ -1798,28 +1798,28 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>2.44</v>
+        <v>1.16</v>
       </c>
       <c r="C24">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E24">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>9205</v>
+        <v>11521</v>
       </c>
     </row>
     <row r="25">
@@ -1827,28 +1827,28 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>2.39</v>
+        <v>1.11</v>
       </c>
       <c r="C25">
-        <v>0.0011</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>19</v>
+        <v>18.34</v>
       </c>
       <c r="E25">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>2.04</v>
       </c>
       <c r="I25">
-        <v>8744</v>
+        <v>11393</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_monthly_visits_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_monthly_visits_Raw.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -388,7 +388,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>median_visits</t>
+          <t>median_visitst</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -398,7 +398,22 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>n_pts</t>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>upper</t>
         </is>
       </c>
     </row>
@@ -407,7 +422,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -416,7 +431,7 @@
         <v>23</v>
       </c>
       <c r="E2">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -428,7 +443,16 @@
         <v>3</v>
       </c>
       <c r="I2">
-        <v>17705</v>
+        <v>22407</v>
+      </c>
+      <c r="J2">
+        <v>0.02</v>
+      </c>
+      <c r="K2">
+        <v>2.39</v>
+      </c>
+      <c r="L2">
+        <v>2.46</v>
       </c>
     </row>
     <row r="3">
@@ -436,28 +460,37 @@
         <v>2</v>
       </c>
       <c r="B3">
+        <v>1.68</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>25</v>
+      </c>
+      <c r="E3">
+        <v>2.13</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>22407</v>
+      </c>
+      <c r="J3">
+        <v>0.01</v>
+      </c>
+      <c r="K3">
         <v>1.66</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>27</v>
-      </c>
-      <c r="E3">
-        <v>2.24</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>15672</v>
+      <c r="L3">
+        <v>1.71</v>
       </c>
     </row>
     <row r="4">
@@ -465,16 +498,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -486,7 +519,16 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>14748</v>
+        <v>22407</v>
+      </c>
+      <c r="J4">
+        <v>0.01</v>
+      </c>
+      <c r="K4">
+        <v>1.5</v>
+      </c>
+      <c r="L4">
+        <v>1.56</v>
       </c>
     </row>
     <row r="5">
@@ -494,16 +536,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -515,7 +557,16 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>14258</v>
+        <v>22407</v>
+      </c>
+      <c r="J5">
+        <v>0.01</v>
+      </c>
+      <c r="K5">
+        <v>1.24</v>
+      </c>
+      <c r="L5">
+        <v>1.29</v>
       </c>
     </row>
     <row r="6">
@@ -523,28 +574,37 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6">
-        <v>13929</v>
+        <v>22407</v>
+      </c>
+      <c r="J6">
+        <v>0.01</v>
+      </c>
+      <c r="K6">
+        <v>1.13</v>
+      </c>
+      <c r="L6">
+        <v>1.18</v>
       </c>
     </row>
     <row r="7">
@@ -552,16 +612,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1.29</v>
+        <v>1.03</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E7">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -570,10 +630,19 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>13651</v>
+        <v>22407</v>
+      </c>
+      <c r="J7">
+        <v>0.01</v>
+      </c>
+      <c r="K7">
+        <v>1.01</v>
+      </c>
+      <c r="L7">
+        <v>1.05</v>
       </c>
     </row>
     <row r="8">
@@ -581,16 +650,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1.26</v>
+        <v>0.99</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E8">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -599,10 +668,19 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>13405</v>
+        <v>22407</v>
+      </c>
+      <c r="J8">
+        <v>0.01</v>
+      </c>
+      <c r="K8">
+        <v>0.96</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
       </c>
     </row>
     <row r="9">
@@ -610,16 +688,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1.16</v>
+        <v>0.89</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E9">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -628,10 +706,19 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>13184</v>
+        <v>22407</v>
+      </c>
+      <c r="J9">
+        <v>0.01</v>
+      </c>
+      <c r="K9">
+        <v>0.87</v>
+      </c>
+      <c r="L9">
+        <v>0.91</v>
       </c>
     </row>
     <row r="10">
@@ -639,16 +726,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1.17</v>
+        <v>0.88</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -657,10 +744,19 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>13022</v>
+        <v>22407</v>
+      </c>
+      <c r="J10">
+        <v>0.01</v>
+      </c>
+      <c r="K10">
+        <v>0.86</v>
+      </c>
+      <c r="L10">
+        <v>0.9</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +764,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1.14</v>
+        <v>0.85</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E11">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -686,10 +782,19 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>12853</v>
+        <v>22407</v>
+      </c>
+      <c r="J11">
+        <v>0.01</v>
+      </c>
+      <c r="K11">
+        <v>0.82</v>
+      </c>
+      <c r="L11">
+        <v>0.87</v>
       </c>
     </row>
     <row r="12">
@@ -697,16 +802,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1.09</v>
+        <v>0.79</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E12">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -718,7 +823,16 @@
         <v>1</v>
       </c>
       <c r="I12">
-        <v>12710</v>
+        <v>22407</v>
+      </c>
+      <c r="J12">
+        <v>0.01</v>
+      </c>
+      <c r="K12">
+        <v>0.77</v>
+      </c>
+      <c r="L12">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -726,7 +840,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.12</v>
+        <v>0.82</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -735,7 +849,7 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -744,10 +858,19 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>12552</v>
+        <v>22407</v>
+      </c>
+      <c r="J13">
+        <v>0.01</v>
+      </c>
+      <c r="K13">
+        <v>0.79</v>
+      </c>
+      <c r="L13">
+        <v>0.84</v>
       </c>
     </row>
     <row r="14">
@@ -755,16 +878,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1.05</v>
+        <v>0.75</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E14">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -776,7 +899,16 @@
         <v>1</v>
       </c>
       <c r="I14">
-        <v>12402</v>
+        <v>22407</v>
+      </c>
+      <c r="J14">
+        <v>0.01</v>
+      </c>
+      <c r="K14">
+        <v>0.73</v>
+      </c>
+      <c r="L14">
+        <v>0.77</v>
       </c>
     </row>
     <row r="15">
@@ -784,16 +916,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1.04</v>
+        <v>0.74</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E15">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -805,7 +937,16 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <v>12259</v>
+        <v>22407</v>
+      </c>
+      <c r="J15">
+        <v>0.01</v>
+      </c>
+      <c r="K15">
+        <v>0.72</v>
+      </c>
+      <c r="L15">
+        <v>0.76</v>
       </c>
     </row>
     <row r="16">
@@ -813,16 +954,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E16">
-        <v>1.84</v>
+        <v>1.54</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -834,7 +975,16 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>12141</v>
+        <v>22407</v>
+      </c>
+      <c r="J16">
+        <v>0.01</v>
+      </c>
+      <c r="K16">
+        <v>0.68</v>
+      </c>
+      <c r="L16">
+        <v>0.72</v>
       </c>
     </row>
     <row r="17">
@@ -842,7 +992,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.98</v>
+        <v>0.67</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -851,7 +1001,7 @@
         <v>20</v>
       </c>
       <c r="E17">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -863,7 +1013,16 @@
         <v>1</v>
       </c>
       <c r="I17">
-        <v>12018</v>
+        <v>22407</v>
+      </c>
+      <c r="J17">
+        <v>0.01</v>
+      </c>
+      <c r="K17">
+        <v>0.65</v>
+      </c>
+      <c r="L17">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -871,7 +1030,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.93</v>
+        <v>0.64</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -880,7 +1039,7 @@
         <v>17</v>
       </c>
       <c r="E18">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -892,7 +1051,16 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>11896</v>
+        <v>22407</v>
+      </c>
+      <c r="J18">
+        <v>0.01</v>
+      </c>
+      <c r="K18">
+        <v>0.62</v>
+      </c>
+      <c r="L18">
+        <v>0.66</v>
       </c>
     </row>
     <row r="19">
@@ -900,16 +1068,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.95</v>
+        <v>0.63</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E19">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -921,7 +1089,16 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>11767</v>
+        <v>22407</v>
+      </c>
+      <c r="J19">
+        <v>0.01</v>
+      </c>
+      <c r="K19">
+        <v>0.61</v>
+      </c>
+      <c r="L19">
+        <v>0.64</v>
       </c>
     </row>
     <row r="20">
@@ -929,7 +1106,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -938,7 +1115,7 @@
         <v>25</v>
       </c>
       <c r="E20">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -950,7 +1127,16 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>11657</v>
+        <v>22407</v>
+      </c>
+      <c r="J20">
+        <v>0.01</v>
+      </c>
+      <c r="K20">
+        <v>0.6</v>
+      </c>
+      <c r="L20">
+        <v>0.64</v>
       </c>
     </row>
     <row r="21">
@@ -958,7 +1144,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.86</v>
+        <v>0.58</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -967,7 +1153,7 @@
         <v>20</v>
       </c>
       <c r="E21">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -976,10 +1162,19 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>11530</v>
+        <v>22407</v>
+      </c>
+      <c r="J21">
+        <v>0.01</v>
+      </c>
+      <c r="K21">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="L21">
+        <v>0.59</v>
       </c>
     </row>
     <row r="22">
@@ -987,7 +1182,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.9</v>
+        <v>0.59</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -996,7 +1191,7 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1005,10 +1200,19 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>11401</v>
+        <v>22407</v>
+      </c>
+      <c r="J22">
+        <v>0.01</v>
+      </c>
+      <c r="K22">
+        <v>0.57</v>
+      </c>
+      <c r="L22">
+        <v>0.61</v>
       </c>
     </row>
     <row r="23">
@@ -1016,7 +1220,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.83</v>
+        <v>0.53</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1025,7 +1229,7 @@
         <v>21</v>
       </c>
       <c r="E23">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1034,10 +1238,19 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>11281</v>
+        <v>22407</v>
+      </c>
+      <c r="J23">
+        <v>0.01</v>
+      </c>
+      <c r="K23">
+        <v>0.52</v>
+      </c>
+      <c r="L23">
+        <v>0.55</v>
       </c>
     </row>
     <row r="24">
@@ -1045,16 +1258,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.85</v>
+        <v>0.55</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E24">
-        <v>1.72</v>
+        <v>1.38</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1063,10 +1276,19 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>11166</v>
+        <v>22407</v>
+      </c>
+      <c r="J24">
+        <v>0.01</v>
+      </c>
+      <c r="K24">
+        <v>0.53</v>
+      </c>
+      <c r="L24">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1074,16 +1296,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.61</v>
+        <v>0.5</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E25">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1095,7 +1317,16 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>7244</v>
+        <v>22407</v>
+      </c>
+      <c r="J25">
+        <v>0.01</v>
+      </c>
+      <c r="K25">
+        <v>0.48</v>
+      </c>
+      <c r="L25">
+        <v>0.51</v>
       </c>
     </row>
   </sheetData>
@@ -1175,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1184,7 +1415,7 @@
         <v>23</v>
       </c>
       <c r="E2">
-        <v>2.61</v>
+        <v>2.48</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1193,19 +1424,19 @@
         <v>2</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I2">
-        <v>16978</v>
+        <v>22407</v>
       </c>
       <c r="J2">
         <v>0.02</v>
       </c>
       <c r="K2">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="L2">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="3">
@@ -1213,16 +1444,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1234,16 +1465,16 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>16978</v>
+        <v>21922</v>
       </c>
       <c r="J3">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="K3">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="L3">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="4">
@@ -1251,16 +1482,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1272,16 +1503,16 @@
         <v>2</v>
       </c>
       <c r="I4">
-        <v>16978</v>
+        <v>21014</v>
       </c>
       <c r="J4">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="K4">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="L4">
-        <v>1.48</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="5">
@@ -1289,37 +1520,37 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>2</v>
       </c>
       <c r="I5">
-        <v>16978</v>
+        <v>19680</v>
       </c>
       <c r="J5">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="K5">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="L5">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="6">
@@ -1327,13 +1558,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>2.02</v>
@@ -1342,22 +1573,22 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>2</v>
       </c>
       <c r="I6">
-        <v>16978</v>
+        <v>18513</v>
       </c>
       <c r="J6">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="K6">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="L6">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="7">
@@ -1365,37 +1596,37 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E7">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>16978</v>
+        <v>17683</v>
       </c>
       <c r="J7">
         <v>0.01</v>
       </c>
       <c r="K7">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="L7">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="8">
@@ -1403,37 +1634,37 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E8">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>16978</v>
+        <v>17019</v>
       </c>
       <c r="J8">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K8">
-        <v>0.99</v>
+        <v>1.27</v>
       </c>
       <c r="L8">
-        <v>1.04</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="9">
@@ -1441,37 +1672,37 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.92</v>
+        <v>1.22</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E9">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>16978</v>
+        <v>16420</v>
       </c>
       <c r="J9">
         <v>0.01</v>
       </c>
       <c r="K9">
-        <v>0.89</v>
+        <v>1.19</v>
       </c>
       <c r="L9">
-        <v>0.95</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="10">
@@ -1479,37 +1710,37 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.91</v>
+        <v>1.24</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>16978</v>
+        <v>15897</v>
       </c>
       <c r="J10">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K10">
-        <v>0.88</v>
+        <v>1.21</v>
       </c>
       <c r="L10">
-        <v>0.9399999999999999</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="11">
@@ -1517,37 +1748,37 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.87</v>
+        <v>1.23</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E11">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>16978</v>
+        <v>15352</v>
       </c>
       <c r="J11">
         <v>0.01</v>
       </c>
       <c r="K11">
-        <v>0.85</v>
+        <v>1.2</v>
       </c>
       <c r="L11">
-        <v>0.9</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="12">
@@ -1555,16 +1786,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.83</v>
+        <v>1.19</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E12">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1573,19 +1804,19 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>16978</v>
+        <v>14894</v>
       </c>
       <c r="J12">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K12">
-        <v>0.8</v>
+        <v>1.16</v>
       </c>
       <c r="L12">
-        <v>0.85</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="13">
@@ -1593,7 +1824,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.84</v>
+        <v>1.26</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1602,28 +1833,28 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>16978</v>
+        <v>14453</v>
       </c>
       <c r="J13">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K13">
-        <v>0.82</v>
+        <v>1.23</v>
       </c>
       <c r="L13">
-        <v>0.87</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="14">
@@ -1631,16 +1862,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.78</v>
+        <v>1.2</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E14">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1649,19 +1880,19 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14">
-        <v>16978</v>
+        <v>13971</v>
       </c>
       <c r="J14">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K14">
-        <v>0.75</v>
+        <v>1.17</v>
       </c>
       <c r="L14">
-        <v>0.8</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="15">
@@ -1669,16 +1900,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.76</v>
+        <v>1.22</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>19</v>
+        <v>21.67</v>
       </c>
       <c r="E15">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1687,19 +1918,19 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>16978</v>
+        <v>13573</v>
       </c>
       <c r="J15">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K15">
-        <v>0.74</v>
+        <v>1.19</v>
       </c>
       <c r="L15">
-        <v>0.79</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="16">
@@ -1707,16 +1938,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.72</v>
+        <v>1.2</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E16">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1725,19 +1956,19 @@
         <v>0</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>16978</v>
+        <v>13156</v>
       </c>
       <c r="J16">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K16">
-        <v>0.7</v>
+        <v>1.16</v>
       </c>
       <c r="L16">
-        <v>0.75</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="17">
@@ -1745,16 +1976,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.7</v>
+        <v>1.18</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>20</v>
+        <v>21.44</v>
       </c>
       <c r="E17">
-        <v>1.59</v>
+        <v>1.84</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1763,19 +1994,19 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>16978</v>
+        <v>12733</v>
       </c>
       <c r="J17">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K17">
-        <v>0.68</v>
+        <v>1.15</v>
       </c>
       <c r="L17">
-        <v>0.73</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="18">
@@ -1783,7 +2014,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.67</v>
+        <v>1.16</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1792,7 +2023,7 @@
         <v>17</v>
       </c>
       <c r="E18">
-        <v>1.51</v>
+        <v>1.77</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1801,19 +2032,19 @@
         <v>0</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>16978</v>
+        <v>12334</v>
       </c>
       <c r="J18">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K18">
-        <v>0.64</v>
+        <v>1.13</v>
       </c>
       <c r="L18">
-        <v>0.6899999999999999</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="19">
@@ -1821,16 +2052,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.66</v>
+        <v>1.17</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E19">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1839,19 +2070,19 @@
         <v>0</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>16978</v>
+        <v>11979</v>
       </c>
       <c r="J19">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K19">
-        <v>0.64</v>
+        <v>1.14</v>
       </c>
       <c r="L19">
-        <v>0.6899999999999999</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="20">
@@ -1859,7 +2090,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.64</v>
+        <v>1.19</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1868,7 +2099,7 @@
         <v>25</v>
       </c>
       <c r="E20">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1877,19 +2108,19 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20">
-        <v>16978</v>
+        <v>11635</v>
       </c>
       <c r="J20">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K20">
-        <v>0.62</v>
+        <v>1.16</v>
       </c>
       <c r="L20">
-        <v>0.66</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="21">
@@ -1897,7 +2128,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.59</v>
+        <v>1.14</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1906,7 +2137,7 @@
         <v>20</v>
       </c>
       <c r="E21">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1915,19 +2146,19 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21">
-        <v>16978</v>
+        <v>11288</v>
       </c>
       <c r="J21">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K21">
-        <v>0.57</v>
+        <v>1.11</v>
       </c>
       <c r="L21">
-        <v>0.62</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="22">
@@ -1935,7 +2166,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.62</v>
+        <v>1.21</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1944,7 +2175,7 @@
         <v>21</v>
       </c>
       <c r="E22">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1953,19 +2184,19 @@
         <v>0</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22">
-        <v>16978</v>
+        <v>10919</v>
       </c>
       <c r="J22">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K22">
-        <v>0.59</v>
+        <v>1.17</v>
       </c>
       <c r="L22">
-        <v>0.64</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="23">
@@ -1973,7 +2204,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.5600000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1982,7 +2213,7 @@
         <v>21</v>
       </c>
       <c r="E23">
-        <v>1.43</v>
+        <v>1.77</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1991,19 +2222,19 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>16978</v>
+        <v>10562</v>
       </c>
       <c r="J23">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K23">
-        <v>0.54</v>
+        <v>1.1</v>
       </c>
       <c r="L23">
-        <v>0.58</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="24">
@@ -2011,16 +2242,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.57</v>
+        <v>1.2</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E24">
-        <v>1.46</v>
+        <v>1.86</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -2029,19 +2260,19 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>16978</v>
+        <v>10215</v>
       </c>
       <c r="J24">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K24">
-        <v>0.54</v>
+        <v>1.16</v>
       </c>
       <c r="L24">
-        <v>0.59</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="25">
@@ -2049,16 +2280,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.52</v>
+        <v>1.14</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>20.37</v>
+        <v>19.36</v>
       </c>
       <c r="E25">
-        <v>1.41</v>
+        <v>1.84</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -2067,19 +2298,19 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="I25">
-        <v>16978</v>
+        <v>9900</v>
       </c>
       <c r="J25">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K25">
-        <v>0.5</v>
+        <v>1.11</v>
       </c>
       <c r="L25">
-        <v>0.54</v>
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_monthly_visits_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_monthly_visits_Raw.xlsx
@@ -422,16 +422,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.42</v>
+        <v>3.19</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="E2">
-        <v>2.48</v>
+        <v>3.73</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -440,19 +440,19 @@
         <v>2</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J2">
         <v>0.02</v>
       </c>
       <c r="K2">
-        <v>2.39</v>
+        <v>3.14</v>
       </c>
       <c r="L2">
-        <v>2.46</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="3">
@@ -460,16 +460,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="E3">
-        <v>2.13</v>
+        <v>3.2</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -478,19 +478,19 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K3">
-        <v>1.66</v>
+        <v>2.21</v>
       </c>
       <c r="L3">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4">
@@ -498,16 +498,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="E4">
-        <v>2.13</v>
+        <v>3.25</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -516,19 +516,19 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J4">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K4">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="L4">
-        <v>1.56</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.27</v>
+        <v>1.71</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E5">
-        <v>1.89</v>
+        <v>2.81</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -557,16 +557,16 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J5">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K5">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="L5">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="6">
@@ -574,16 +574,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.15</v>
+        <v>1.58</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="E6">
-        <v>1.89</v>
+        <v>2.85</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -595,16 +595,16 @@
         <v>2</v>
       </c>
       <c r="I6">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J6">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K6">
-        <v>1.13</v>
+        <v>1.54</v>
       </c>
       <c r="L6">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="7">
@@ -612,16 +612,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E7">
-        <v>1.78</v>
+        <v>2.69</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -630,19 +630,19 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J7">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K7">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="L7">
-        <v>1.05</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="8">
@@ -650,16 +650,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.99</v>
+        <v>1.35</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="E8">
-        <v>1.79</v>
+        <v>2.7</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -668,19 +668,19 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J8">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K8">
-        <v>0.96</v>
+        <v>1.32</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="9">
@@ -688,16 +688,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.89</v>
+        <v>1.24</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E9">
-        <v>1.66</v>
+        <v>2.52</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -709,16 +709,16 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J9">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K9">
-        <v>0.87</v>
+        <v>1.2</v>
       </c>
       <c r="L9">
-        <v>0.91</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="10">
@@ -726,16 +726,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.88</v>
+        <v>1.21</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E10">
-        <v>1.69</v>
+        <v>2.53</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -747,16 +747,16 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J10">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K10">
-        <v>0.86</v>
+        <v>1.18</v>
       </c>
       <c r="L10">
-        <v>0.9</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="11">
@@ -764,16 +764,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.85</v>
+        <v>1.17</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>1.63</v>
+        <v>2.43</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -785,16 +785,16 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J11">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K11">
-        <v>0.82</v>
+        <v>1.14</v>
       </c>
       <c r="L11">
-        <v>0.87</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12">
@@ -802,16 +802,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.79</v>
+        <v>1.09</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E12">
-        <v>1.6</v>
+        <v>2.38</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -823,16 +823,16 @@
         <v>1</v>
       </c>
       <c r="I12">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J12">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K12">
-        <v>0.77</v>
+        <v>1.05</v>
       </c>
       <c r="L12">
-        <v>0.8100000000000001</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="13">
@@ -840,16 +840,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.82</v>
+        <v>1.13</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E13">
-        <v>1.66</v>
+        <v>2.52</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -861,16 +861,16 @@
         <v>1</v>
       </c>
       <c r="I13">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J13">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K13">
-        <v>0.79</v>
+        <v>1.1</v>
       </c>
       <c r="L13">
-        <v>0.84</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="14">
@@ -878,16 +878,16 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="E14">
-        <v>1.55</v>
+        <v>2.36</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>1</v>
       </c>
       <c r="I14">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J14">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K14">
-        <v>0.73</v>
+        <v>1.01</v>
       </c>
       <c r="L14">
-        <v>0.77</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="15">
@@ -916,16 +916,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.74</v>
+        <v>1.02</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E15">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -937,16 +937,16 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J15">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K15">
-        <v>0.72</v>
+        <v>0.99</v>
       </c>
       <c r="L15">
-        <v>0.76</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="16">
@@ -954,16 +954,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.7</v>
+        <v>0.97</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E16">
-        <v>1.54</v>
+        <v>2.34</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -975,16 +975,16 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J16">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K16">
-        <v>0.68</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L16">
-        <v>0.72</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -992,16 +992,16 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.67</v>
+        <v>0.93</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E17">
-        <v>1.5</v>
+        <v>2.26</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1013,16 +1013,16 @@
         <v>1</v>
       </c>
       <c r="I17">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J17">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K17">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="L17">
-        <v>0.6899999999999999</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="18">
@@ -1030,16 +1030,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="E18">
-        <v>1.43</v>
+        <v>2.18</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1051,16 +1051,16 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J18">
         <v>0.01</v>
       </c>
       <c r="K18">
-        <v>0.62</v>
+        <v>0.86</v>
       </c>
       <c r="L18">
-        <v>0.66</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="19">
@@ -1068,16 +1068,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.63</v>
+        <v>0.87</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="E19">
-        <v>1.46</v>
+        <v>2.21</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1089,16 +1089,16 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J19">
         <v>0.01</v>
       </c>
       <c r="K19">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="L19">
-        <v>0.64</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="20">
@@ -1106,16 +1106,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.62</v>
+        <v>0.87</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="E20">
-        <v>1.46</v>
+        <v>2.23</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1127,16 +1127,16 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J20">
         <v>0.01</v>
       </c>
       <c r="K20">
-        <v>0.6</v>
+        <v>0.84</v>
       </c>
       <c r="L20">
-        <v>0.64</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21">
@@ -1144,16 +1144,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E21">
-        <v>1.4</v>
+        <v>2.13</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -1162,19 +1162,19 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J21">
         <v>0.01</v>
       </c>
       <c r="K21">
-        <v>0.5600000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="L21">
-        <v>0.59</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="22">
@@ -1182,16 +1182,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0.59</v>
+        <v>0.82</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="E22">
-        <v>1.44</v>
+        <v>2.22</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1203,16 +1203,16 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J22">
         <v>0.01</v>
       </c>
       <c r="K22">
-        <v>0.57</v>
+        <v>0.8</v>
       </c>
       <c r="L22">
-        <v>0.61</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="23">
@@ -1220,16 +1220,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E23">
-        <v>1.34</v>
+        <v>2.06</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J23">
         <v>0.01</v>
       </c>
       <c r="K23">
-        <v>0.52</v>
+        <v>0.72</v>
       </c>
       <c r="L23">
-        <v>0.55</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="24">
@@ -1258,16 +1258,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0.55</v>
+        <v>0.76</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E24">
-        <v>1.38</v>
+        <v>2.07</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1279,16 +1279,16 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J24">
         <v>0.01</v>
       </c>
       <c r="K24">
-        <v>0.53</v>
+        <v>0.73</v>
       </c>
       <c r="L24">
-        <v>0.5600000000000001</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="25">
@@ -1296,16 +1296,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E25">
-        <v>1.32</v>
+        <v>2.03</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1317,16 +1317,16 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J25">
         <v>0.01</v>
       </c>
       <c r="K25">
-        <v>0.48</v>
+        <v>0.68</v>
       </c>
       <c r="L25">
-        <v>0.51</v>
+        <v>0.73</v>
       </c>
     </row>
   </sheetData>
@@ -1406,16 +1406,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.42</v>
+        <v>3.19</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="E2">
-        <v>2.48</v>
+        <v>3.73</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1424,19 +1424,19 @@
         <v>2</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>22407</v>
+        <v>22462</v>
       </c>
       <c r="J2">
         <v>0.02</v>
       </c>
       <c r="K2">
-        <v>2.39</v>
+        <v>3.14</v>
       </c>
       <c r="L2">
-        <v>2.46</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="3">
@@ -1444,16 +1444,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1.71</v>
+        <v>2.29</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="E3">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1462,19 +1462,19 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>21922</v>
+        <v>21973</v>
       </c>
       <c r="J3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K3">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="L3">
-        <v>1.74</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="4">
@@ -1482,16 +1482,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.63</v>
+        <v>2.21</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="E4">
-        <v>2.17</v>
+        <v>3.32</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1500,19 +1500,19 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>21014</v>
+        <v>21056</v>
       </c>
       <c r="J4">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K4">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="L4">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="5">
@@ -1520,16 +1520,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.42</v>
+        <v>1.93</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E5">
-        <v>1.99</v>
+        <v>2.96</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1538,19 +1538,19 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>19680</v>
+        <v>19708</v>
       </c>
       <c r="J5">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K5">
-        <v>1.39</v>
+        <v>1.89</v>
       </c>
       <c r="L5">
-        <v>1.45</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="6">
@@ -1558,16 +1558,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>1.39</v>
+        <v>1.91</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="E6">
-        <v>2.02</v>
+        <v>3.06</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1576,19 +1576,19 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>18513</v>
+        <v>18537</v>
       </c>
       <c r="J6">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K6">
-        <v>1.36</v>
+        <v>1.86</v>
       </c>
       <c r="L6">
-        <v>1.42</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="7">
@@ -1596,16 +1596,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="E7">
-        <v>1.93</v>
+        <v>2.93</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -1617,16 +1617,16 @@
         <v>2</v>
       </c>
       <c r="I7">
-        <v>17683</v>
+        <v>17706</v>
       </c>
       <c r="J7">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K7">
-        <v>1.27</v>
+        <v>1.74</v>
       </c>
       <c r="L7">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="8">
@@ -1634,16 +1634,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="E8">
-        <v>1.97</v>
+        <v>2.99</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1655,16 +1655,16 @@
         <v>2</v>
       </c>
       <c r="I8">
-        <v>17019</v>
+        <v>17039</v>
       </c>
       <c r="J8">
         <v>0.02</v>
       </c>
       <c r="K8">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="L8">
-        <v>1.33</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="9">
@@ -1672,16 +1672,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="E9">
-        <v>1.85</v>
+        <v>2.83</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1693,16 +1693,16 @@
         <v>2</v>
       </c>
       <c r="I9">
-        <v>16420</v>
+        <v>16440</v>
       </c>
       <c r="J9">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K9">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
       <c r="L9">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="10">
@@ -1710,16 +1710,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E10">
-        <v>1.89</v>
+        <v>2.88</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1731,16 +1731,16 @@
         <v>2</v>
       </c>
       <c r="I10">
-        <v>15897</v>
+        <v>15916</v>
       </c>
       <c r="J10">
         <v>0.02</v>
       </c>
       <c r="K10">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="L10">
-        <v>1.27</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="11">
@@ -1748,16 +1748,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>1.23</v>
+        <v>1.71</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E11">
-        <v>1.85</v>
+        <v>2.79</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1769,16 +1769,16 @@
         <v>2</v>
       </c>
       <c r="I11">
-        <v>15352</v>
+        <v>15368</v>
       </c>
       <c r="J11">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K11">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="L11">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="12">
@@ -1786,37 +1786,37 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>1.19</v>
+        <v>1.63</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E12">
-        <v>1.85</v>
+        <v>2.78</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>2</v>
       </c>
       <c r="I12">
-        <v>14894</v>
+        <v>14910</v>
       </c>
       <c r="J12">
         <v>0.02</v>
       </c>
       <c r="K12">
-        <v>1.16</v>
+        <v>1.59</v>
       </c>
       <c r="L12">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="13">
@@ -1824,16 +1824,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E13">
-        <v>1.93</v>
+        <v>2.97</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1845,16 +1845,16 @@
         <v>2</v>
       </c>
       <c r="I13">
-        <v>14453</v>
+        <v>14467</v>
       </c>
       <c r="J13">
         <v>0.02</v>
       </c>
       <c r="K13">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="L13">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="14">
@@ -1862,37 +1862,37 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="E14">
-        <v>1.83</v>
+        <v>2.82</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>2</v>
       </c>
       <c r="I14">
-        <v>13971</v>
+        <v>13984</v>
       </c>
       <c r="J14">
         <v>0.02</v>
       </c>
       <c r="K14">
-        <v>1.17</v>
+        <v>1.62</v>
       </c>
       <c r="L14">
-        <v>1.23</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="15">
@@ -1900,37 +1900,37 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>21.67</v>
+        <v>36.12</v>
       </c>
       <c r="E15">
-        <v>1.88</v>
+        <v>2.82</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <v>2</v>
       </c>
       <c r="I15">
-        <v>13573</v>
+        <v>13586</v>
       </c>
       <c r="J15">
         <v>0.02</v>
       </c>
       <c r="K15">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
       <c r="L15">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="16">
@@ -1938,16 +1938,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E16">
-        <v>1.87</v>
+        <v>2.88</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1959,16 +1959,16 @@
         <v>2</v>
       </c>
       <c r="I16">
-        <v>13156</v>
+        <v>13168</v>
       </c>
       <c r="J16">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K16">
-        <v>1.16</v>
+        <v>1.61</v>
       </c>
       <c r="L16">
-        <v>1.23</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="17">
@@ -1976,37 +1976,37 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>1.18</v>
+        <v>1.64</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>21.44</v>
+        <v>44</v>
       </c>
       <c r="E17">
-        <v>1.84</v>
+        <v>2.81</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <v>2</v>
       </c>
       <c r="I17">
-        <v>12733</v>
+        <v>12743</v>
       </c>
       <c r="J17">
         <v>0.02</v>
       </c>
       <c r="K17">
-        <v>1.15</v>
+        <v>1.59</v>
       </c>
       <c r="L17">
-        <v>1.22</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="18">
@@ -2014,16 +2014,16 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="E18">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -2035,16 +2035,16 @@
         <v>2</v>
       </c>
       <c r="I18">
-        <v>12334</v>
+        <v>12343</v>
       </c>
       <c r="J18">
         <v>0.02</v>
       </c>
       <c r="K18">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="L18">
-        <v>1.19</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="19">
@@ -2052,16 +2052,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>1.17</v>
+        <v>1.63</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="E19">
-        <v>1.84</v>
+        <v>2.82</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -2073,16 +2073,16 @@
         <v>2</v>
       </c>
       <c r="I19">
-        <v>11979</v>
+        <v>11988</v>
       </c>
       <c r="J19">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K19">
-        <v>1.14</v>
+        <v>1.58</v>
       </c>
       <c r="L19">
-        <v>1.2</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="20">
@@ -2090,37 +2090,37 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>1.19</v>
+        <v>1.68</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="E20">
-        <v>1.86</v>
+        <v>2.89</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>2</v>
       </c>
       <c r="I20">
-        <v>11635</v>
+        <v>11643</v>
       </c>
       <c r="J20">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K20">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="L20">
-        <v>1.23</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="21">
@@ -2128,16 +2128,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>1.14</v>
+        <v>1.59</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E21">
-        <v>1.81</v>
+        <v>2.8</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2149,16 +2149,16 @@
         <v>2</v>
       </c>
       <c r="I21">
-        <v>11288</v>
+        <v>11294</v>
       </c>
       <c r="J21">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K21">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="L21">
-        <v>1.17</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="22">
@@ -2166,37 +2166,37 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>1.21</v>
+        <v>1.69</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="E22">
-        <v>1.89</v>
+        <v>2.95</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
         <v>2</v>
       </c>
       <c r="I22">
-        <v>10919</v>
+        <v>10925</v>
       </c>
       <c r="J22">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K22">
-        <v>1.17</v>
+        <v>1.64</v>
       </c>
       <c r="L22">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="23">
@@ -2204,16 +2204,16 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>1.13</v>
+        <v>1.59</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E23">
-        <v>1.77</v>
+        <v>2.78</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -2225,16 +2225,16 @@
         <v>2</v>
       </c>
       <c r="I23">
-        <v>10562</v>
+        <v>10568</v>
       </c>
       <c r="J23">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K23">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="L23">
-        <v>1.16</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="24">
@@ -2242,37 +2242,37 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E24">
-        <v>1.86</v>
+        <v>2.82</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>2</v>
       </c>
       <c r="I24">
-        <v>10215</v>
+        <v>10221</v>
       </c>
       <c r="J24">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K24">
-        <v>1.16</v>
+        <v>1.61</v>
       </c>
       <c r="L24">
-        <v>1.23</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="25">
@@ -2280,16 +2280,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>1.14</v>
+        <v>1.63</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>19.36</v>
+        <v>58.07</v>
       </c>
       <c r="E25">
-        <v>1.84</v>
+        <v>2.88</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -2301,16 +2301,16 @@
         <v>2.04</v>
       </c>
       <c r="I25">
-        <v>9900</v>
+        <v>9906</v>
       </c>
       <c r="J25">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K25">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="L25">
-        <v>1.18</v>
+        <v>1.68</v>
       </c>
     </row>
   </sheetData>
